--- a/assets/constructions/examples/ctd_bs_carti_indexable.xlsx
+++ b/assets/constructions/examples/ctd_bs_carti_indexable.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X6"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TBS913-48-L</t>
+          <t>CBS910-36-L</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -563,19 +583,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TBS</t>
+          <t>CBS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F2" t="n">
         <v>50</v>
-      </c>
-      <c r="F2" t="n">
-        <v>70</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
@@ -590,18 +610,18 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>ISO_5610:13X13</t>
+          <t>ISO_5610:10X10</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>ISO_TP1103H</t>
+          <t>ISO_CC0602H</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>TP1103H</t>
+          <t>CC0602H</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -611,7 +631,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>C</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -619,7 +639,7 @@
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -628,12 +648,26 @@
         <is>
           <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
         </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>34.34</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>2814.98</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CBS919-85-L</t>
+          <t>DR1620-65</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -641,21 +675,21 @@
           <t>DEREK</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CBS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>16</v>
+      </c>
       <c r="E3" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>115</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="G3" t="n">
+        <v>65</v>
+      </c>
       <c r="H3" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
@@ -663,25 +697,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>ISO_5610:19X19</t>
+          <t>HB-16</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>ISO_CC1204H</t>
+          <t>ISO_TP1103LH</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>CC1204H</t>
+          <t>TP1103LH</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -691,7 +725,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>T</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -699,7 +733,7 @@
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.28</v>
+        <v>0.16</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -708,12 +742,26 @@
         <is>
           <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
         </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>4037.21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DBJ2020-83</t>
+          <t>DBJ1016-45</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -723,17 +771,19 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F4" t="n">
         <v>20</v>
       </c>
-      <c r="E4" t="n">
-        <v>26</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="H4" t="n">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
@@ -748,18 +798,18 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>HB-20</t>
+          <t>HB-10</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>ISO_TP1103H</t>
+          <t>ISO_TP0902H</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>TP1103H</t>
+          <t>TP0902H</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -777,7 +827,7 @@
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -786,62 +836,84 @@
         <is>
           <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
         </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>57.94</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>4749.57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CBS408-30</t>
+          <t>IHAXF 8-10-AVI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>ISCAR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CBS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>IHAXF-AVI</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>16</v>
+      </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>38</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>48</v>
+      </c>
       <c r="H5" t="n">
-        <v>30</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="I5" t="n">
+        <v>70</v>
+      </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>HS</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
       <c r="M5" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ISO_5610:8X8</t>
+          <t>DAN_HB-16</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ISO_CC0602H</t>
+          <t>ISO_WC0201H</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>CC0602H</t>
+          <t>WC0201H</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -851,29 +923,33 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W</t>
         </is>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
-        </is>
-      </c>
+          <t>2020 / www.iscar.com</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SB-C32-TB45-200</t>
+          <t>SB-C32-TB42-200</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -887,7 +963,7 @@
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>44.8</v>
+        <v>41.8</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
@@ -944,6 +1020,20 @@
         <is>
           <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
         </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>102.97</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>8440.85</v>
       </c>
     </row>
   </sheetData>
